--- a/datos/CUOTAS DISTRIBUIDORES Q4 PLATAFORMA CONVENIOS (3).xlsx
+++ b/datos/CUOTAS DISTRIBUIDORES Q4 PLATAFORMA CONVENIOS (3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E583B9C-468B-41FD-8E4E-30596D6BE51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A89BA81-932E-4351-B2EE-88F429E77A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EE924088-8CDA-4239-A437-15947D588218}"/>
   </bookViews>
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4071" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4071" uniqueCount="202">
   <si>
     <t>DISTRIBUIDOR</t>
   </si>
@@ -1045,6 +1045,12 @@
   <si>
     <t>Suma de OCTUBRE</t>
   </si>
+  <si>
+    <t xml:space="preserve">ANCHUNDIA BAJANA </t>
+  </si>
+  <si>
+    <t>ANCHUNDIA BAJANAA MIRELLA LUCIA</t>
+  </si>
 </sst>
 </file>
 
@@ -10175,7 +10181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8D923C-FBE4-455B-BC9C-7957F0721F03}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A2:P578"/>
@@ -10236,7 +10242,7 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
     </row>
-    <row r="3" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>189</v>
       </c>
@@ -10270,7 +10276,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>189</v>
       </c>
@@ -10304,7 +10310,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>189</v>
       </c>
@@ -10338,7 +10344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
         <v>189</v>
       </c>
@@ -10372,7 +10378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
         <v>189</v>
       </c>
@@ -10383,7 +10389,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="9"/>
@@ -10406,7 +10412,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="33" t="s">
         <v>189</v>
       </c>
@@ -10417,7 +10423,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="9"/>
@@ -10440,7 +10446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
         <v>189</v>
       </c>
@@ -10474,7 +10480,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="33" t="s">
         <v>189</v>
       </c>
@@ -10512,7 +10518,7 @@
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
     </row>
-    <row r="11" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>189</v>
       </c>
@@ -10550,7 +10556,7 @@
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="33" t="s">
         <v>189</v>
       </c>
@@ -10588,7 +10594,7 @@
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="33" t="s">
         <v>189</v>
       </c>
@@ -10626,7 +10632,7 @@
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
         <v>189</v>
       </c>
@@ -10664,7 +10670,7 @@
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
     </row>
-    <row r="15" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>189</v>
       </c>
@@ -10702,7 +10708,7 @@
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
     </row>
-    <row r="16" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="33" t="s">
         <v>189</v>
       </c>
@@ -10740,7 +10746,7 @@
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
     </row>
-    <row r="17" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33" t="s">
         <v>189</v>
       </c>
@@ -10778,7 +10784,7 @@
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
     </row>
-    <row r="18" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="33" t="s">
         <v>189</v>
       </c>
@@ -10816,7 +10822,7 @@
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
     </row>
-    <row r="19" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="33" t="s">
         <v>189</v>
       </c>
@@ -10854,7 +10860,7 @@
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
     </row>
-    <row r="20" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="33" t="s">
         <v>189</v>
       </c>
@@ -10892,7 +10898,7 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
     </row>
-    <row r="21" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="33" t="s">
         <v>189</v>
       </c>
@@ -10930,7 +10936,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="33" t="s">
         <v>189</v>
       </c>
@@ -10968,7 +10974,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="33" t="s">
         <v>189</v>
       </c>
@@ -11002,7 +11008,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="33" t="s">
         <v>189</v>
       </c>
@@ -11036,7 +11042,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="33" t="s">
         <v>189</v>
       </c>
@@ -11070,7 +11076,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33" t="s">
         <v>189</v>
       </c>
@@ -11104,7 +11110,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33" t="s">
         <v>189</v>
       </c>
@@ -11138,7 +11144,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33" t="s">
         <v>189</v>
       </c>
@@ -11172,7 +11178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33" t="s">
         <v>189</v>
       </c>
@@ -11206,7 +11212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33" t="s">
         <v>189</v>
       </c>
@@ -11240,7 +11246,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>189</v>
       </c>
@@ -11274,7 +11280,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>189</v>
       </c>
@@ -11308,7 +11314,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>189</v>
       </c>
@@ -11342,7 +11348,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>189</v>
       </c>
@@ -11376,7 +11382,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>189</v>
       </c>
@@ -11410,7 +11416,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>189</v>
       </c>
@@ -11444,7 +11450,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33" t="s">
         <v>189</v>
       </c>
@@ -11478,7 +11484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>189</v>
       </c>
@@ -11516,7 +11522,7 @@
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
     </row>
-    <row r="39" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33" t="s">
         <v>189</v>
       </c>
@@ -11554,7 +11560,7 @@
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
     </row>
-    <row r="40" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>189</v>
       </c>
@@ -11592,7 +11598,7 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33" t="s">
         <v>189</v>
       </c>
@@ -11630,7 +11636,7 @@
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
     </row>
-    <row r="42" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
         <v>189</v>
       </c>
@@ -11668,7 +11674,7 @@
       <c r="O42" s="4"/>
       <c r="P42" s="4"/>
     </row>
-    <row r="43" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>189</v>
       </c>
@@ -11702,7 +11708,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33" t="s">
         <v>189</v>
       </c>
@@ -11736,7 +11742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33" t="s">
         <v>189</v>
       </c>
@@ -11770,7 +11776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33" t="s">
         <v>189</v>
       </c>
@@ -11804,7 +11810,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
         <v>189</v>
       </c>
@@ -11838,7 +11844,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33" t="s">
         <v>189</v>
       </c>
@@ -11872,7 +11878,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33" t="s">
         <v>189</v>
       </c>
@@ -11906,7 +11912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33" t="s">
         <v>189</v>
       </c>
@@ -11940,7 +11946,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33" t="s">
         <v>189</v>
       </c>
@@ -11974,7 +11980,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="33" t="s">
         <v>189</v>
       </c>
@@ -12008,7 +12014,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33" t="s">
         <v>189</v>
       </c>
@@ -12042,7 +12048,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="33" t="s">
         <v>189</v>
       </c>
@@ -12076,7 +12082,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="33" t="s">
         <v>189</v>
       </c>
@@ -12110,7 +12116,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="33" t="s">
         <v>189</v>
       </c>
@@ -12144,7 +12150,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="33" t="s">
         <v>189</v>
       </c>
@@ -12178,7 +12184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="33" t="s">
         <v>189</v>
       </c>
@@ -12212,7 +12218,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="33" t="s">
         <v>189</v>
       </c>
@@ -12246,7 +12252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="33" t="s">
         <v>189</v>
       </c>
@@ -12280,7 +12286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="33" t="s">
         <v>189</v>
       </c>
@@ -12314,7 +12320,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="33" t="s">
         <v>189</v>
       </c>
@@ -12348,7 +12354,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="33" t="s">
         <v>189</v>
       </c>
@@ -12382,7 +12388,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>189</v>
       </c>
@@ -12416,7 +12422,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="33" t="s">
         <v>189</v>
       </c>
@@ -12450,7 +12456,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="33" t="s">
         <v>189</v>
       </c>
@@ -12484,7 +12490,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="33" t="s">
         <v>189</v>
       </c>
@@ -12518,7 +12524,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="33" t="s">
         <v>189</v>
       </c>
@@ -12552,7 +12558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="33" t="s">
         <v>189</v>
       </c>
@@ -12586,7 +12592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33" t="s">
         <v>189</v>
       </c>
@@ -12620,7 +12626,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="71" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="33" t="s">
         <v>189</v>
       </c>
@@ -12654,7 +12660,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="33" t="s">
         <v>189</v>
       </c>
@@ -12688,7 +12694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="33" t="s">
         <v>189</v>
       </c>
@@ -12722,7 +12728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="33" t="s">
         <v>189</v>
       </c>
@@ -12756,7 +12762,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="33" t="s">
         <v>189</v>
       </c>
@@ -12790,7 +12796,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="33" t="s">
         <v>189</v>
       </c>
@@ -12824,7 +12830,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="33" t="s">
         <v>189</v>
       </c>
@@ -12858,7 +12864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="33" t="s">
         <v>189</v>
       </c>
@@ -12892,7 +12898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="33" t="s">
         <v>187</v>
       </c>
@@ -12930,7 +12936,7 @@
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
     </row>
-    <row r="80" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>187</v>
       </c>
@@ -12968,7 +12974,7 @@
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
     </row>
-    <row r="81" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="33" t="s">
         <v>187</v>
       </c>
@@ -13006,7 +13012,7 @@
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
     </row>
-    <row r="82" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>187</v>
       </c>
@@ -13044,7 +13050,7 @@
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
     </row>
-    <row r="83" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>187</v>
       </c>
@@ -13078,7 +13084,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="33" t="s">
         <v>187</v>
       </c>
@@ -13112,7 +13118,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="85" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="33" t="s">
         <v>187</v>
       </c>
@@ -13146,7 +13152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="33" t="s">
         <v>187</v>
       </c>
@@ -13180,7 +13186,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="33" t="s">
         <v>187</v>
       </c>
@@ -13214,7 +13220,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="33" t="s">
         <v>187</v>
       </c>
@@ -13248,7 +13254,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="33" t="s">
         <v>187</v>
       </c>
@@ -13282,7 +13288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="33" t="s">
         <v>187</v>
       </c>
@@ -13316,7 +13322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="33" t="s">
         <v>187</v>
       </c>
@@ -13350,7 +13356,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="33" t="s">
         <v>187</v>
       </c>
@@ -13384,7 +13390,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="33" t="s">
         <v>187</v>
       </c>
@@ -13418,7 +13424,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="33" t="s">
         <v>187</v>
       </c>
@@ -13452,7 +13458,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="33" t="s">
         <v>187</v>
       </c>
@@ -13486,7 +13492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="33" t="s">
         <v>187</v>
       </c>
@@ -13520,7 +13526,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="33" t="s">
         <v>187</v>
       </c>
@@ -13554,7 +13560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="33" t="s">
         <v>187</v>
       </c>
@@ -13588,7 +13594,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="33" t="s">
         <v>187</v>
       </c>
@@ -13622,7 +13628,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="33" t="s">
         <v>187</v>
       </c>
@@ -13656,7 +13662,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="33" t="s">
         <v>187</v>
       </c>
@@ -13690,7 +13696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="33" t="s">
         <v>187</v>
       </c>
@@ -13724,7 +13730,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="33" t="s">
         <v>187</v>
       </c>
@@ -13758,7 +13764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="33" t="s">
         <v>187</v>
       </c>
@@ -13792,7 +13798,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="33" t="s">
         <v>187</v>
       </c>
@@ -13826,7 +13832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="33" t="s">
         <v>187</v>
       </c>
@@ -13860,7 +13866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="33" t="s">
         <v>187</v>
       </c>
@@ -13894,7 +13900,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="33" t="s">
         <v>187</v>
       </c>
@@ -13928,7 +13934,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="33" t="s">
         <v>187</v>
       </c>
@@ -13962,7 +13968,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33" t="s">
         <v>187</v>
       </c>
@@ -13996,7 +14002,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="111" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="33" t="s">
         <v>187</v>
       </c>
@@ -14030,7 +14036,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="33" t="s">
         <v>187</v>
       </c>
@@ -14064,7 +14070,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="113" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="33" t="s">
         <v>187</v>
       </c>
@@ -14098,7 +14104,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="114" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="33" t="s">
         <v>187</v>
       </c>
@@ -14132,7 +14138,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="115" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="33" t="s">
         <v>192</v>
       </c>
@@ -14166,7 +14172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="33" t="s">
         <v>192</v>
       </c>
@@ -14200,7 +14206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="33" t="s">
         <v>192</v>
       </c>
@@ -14234,7 +14240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="33" t="s">
         <v>192</v>
       </c>
@@ -14268,7 +14274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="33" t="s">
         <v>192</v>
       </c>
@@ -14302,7 +14308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="33" t="s">
         <v>192</v>
       </c>
@@ -14336,7 +14342,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="33" t="s">
         <v>192</v>
       </c>
@@ -14370,7 +14376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="33" t="s">
         <v>192</v>
       </c>
@@ -14404,7 +14410,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="123" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="33" t="s">
         <v>192</v>
       </c>
@@ -14438,7 +14444,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="33" t="s">
         <v>192</v>
       </c>
@@ -14472,7 +14478,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="33" t="s">
         <v>192</v>
       </c>
@@ -14506,7 +14512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="33" t="s">
         <v>192</v>
       </c>
@@ -14540,7 +14546,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="33" t="s">
         <v>192</v>
       </c>
@@ -14574,7 +14580,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="33" t="s">
         <v>192</v>
       </c>
@@ -14608,7 +14614,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="33" t="s">
         <v>192</v>
       </c>
@@ -14642,7 +14648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="33" t="s">
         <v>192</v>
       </c>
@@ -14676,7 +14682,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="33" t="s">
         <v>192</v>
       </c>
@@ -14710,7 +14716,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="33" t="s">
         <v>192</v>
       </c>
@@ -14744,7 +14750,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="33" t="s">
         <v>192</v>
       </c>
@@ -14778,7 +14784,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="33" t="s">
         <v>192</v>
       </c>
@@ -14812,7 +14818,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="33" t="s">
         <v>192</v>
       </c>
@@ -14846,7 +14852,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="33" t="s">
         <v>192</v>
       </c>
@@ -14880,7 +14886,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="33" t="s">
         <v>192</v>
       </c>
@@ -14914,7 +14920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="33" t="s">
         <v>192</v>
       </c>
@@ -14948,7 +14954,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="33" t="s">
         <v>192</v>
       </c>
@@ -14982,7 +14988,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="33" t="s">
         <v>192</v>
       </c>
@@ -15016,7 +15022,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="33" t="s">
         <v>192</v>
       </c>
@@ -15050,7 +15056,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="33" t="s">
         <v>192</v>
       </c>
@@ -15084,7 +15090,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="33" t="s">
         <v>192</v>
       </c>
@@ -15118,7 +15124,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="33" t="s">
         <v>192</v>
       </c>
@@ -15152,7 +15158,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="33" t="s">
         <v>192</v>
       </c>
@@ -15186,7 +15192,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="33" t="s">
         <v>192</v>
       </c>
@@ -15220,7 +15226,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="147" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="33" t="s">
         <v>192</v>
       </c>
@@ -15254,7 +15260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="33" t="s">
         <v>192</v>
       </c>
@@ -15288,7 +15294,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="33" t="s">
         <v>192</v>
       </c>
@@ -15322,7 +15328,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" s="24" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="33" t="s">
         <v>192</v>
       </c>
@@ -15356,7 +15362,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="33" t="s">
         <v>192</v>
       </c>
@@ -15390,7 +15396,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="33" t="s">
         <v>192</v>
       </c>
@@ -15424,7 +15430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="33" t="s">
         <v>192</v>
       </c>
@@ -15458,7 +15464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="33" t="s">
         <v>192</v>
       </c>
@@ -15492,7 +15498,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="33" t="s">
         <v>192</v>
       </c>
@@ -15526,7 +15532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="33" t="s">
         <v>192</v>
       </c>
@@ -15560,7 +15566,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="33" t="s">
         <v>192</v>
       </c>
@@ -15594,7 +15600,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="33" t="s">
         <v>192</v>
       </c>
@@ -15628,7 +15634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="159" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="33" t="s">
         <v>192</v>
       </c>
@@ -15662,7 +15668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="160" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="33" t="s">
         <v>192</v>
       </c>
@@ -15696,7 +15702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="33" t="s">
         <v>192</v>
       </c>
@@ -15730,7 +15736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" s="13" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="33" t="s">
         <v>192</v>
       </c>
@@ -15764,7 +15770,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="33" t="s">
         <v>192</v>
       </c>
@@ -15798,7 +15804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="33" t="s">
         <v>192</v>
       </c>
@@ -15832,7 +15838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="33" t="s">
         <v>192</v>
       </c>
@@ -15866,7 +15872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="33" t="s">
         <v>192</v>
       </c>
@@ -15900,7 +15906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="33" t="s">
         <v>192</v>
       </c>
@@ -15934,7 +15940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="33" t="s">
         <v>192</v>
       </c>
@@ -15968,7 +15974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="33" t="s">
         <v>192</v>
       </c>
@@ -16002,7 +16008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="33" t="s">
         <v>192</v>
       </c>
@@ -16036,7 +16042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="33" t="s">
         <v>192</v>
       </c>
@@ -16070,7 +16076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="33" t="s">
         <v>192</v>
       </c>
@@ -16104,7 +16110,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="33" t="s">
         <v>192</v>
       </c>
@@ -16138,7 +16144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="33" t="s">
         <v>192</v>
       </c>
@@ -16172,7 +16178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="33" t="s">
         <v>192</v>
       </c>
@@ -16206,7 +16212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="33" t="s">
         <v>192</v>
       </c>
@@ -16240,7 +16246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="33" t="s">
         <v>192</v>
       </c>
@@ -16274,7 +16280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="33" t="s">
         <v>192</v>
       </c>
@@ -16308,7 +16314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="33" t="s">
         <v>192</v>
       </c>
@@ -16342,7 +16348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="33" t="s">
         <v>192</v>
       </c>
@@ -16376,7 +16382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="33" t="s">
         <v>192</v>
       </c>
@@ -16410,7 +16416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="33" t="s">
         <v>192</v>
       </c>
@@ -16444,7 +16450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="33" t="s">
         <v>192</v>
       </c>
@@ -16478,7 +16484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="33" t="s">
         <v>192</v>
       </c>
@@ -16512,7 +16518,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="33" t="s">
         <v>192</v>
       </c>
@@ -16546,7 +16552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="33" t="s">
         <v>192</v>
       </c>
@@ -16580,7 +16586,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="33" t="s">
         <v>192</v>
       </c>
@@ -16614,7 +16620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="33" t="s">
         <v>192</v>
       </c>
@@ -16648,7 +16654,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="33" t="s">
         <v>192</v>
       </c>
@@ -16682,7 +16688,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="33" t="s">
         <v>192</v>
       </c>
@@ -16716,7 +16722,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="33" t="s">
         <v>192</v>
       </c>
@@ -16750,7 +16756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="33" t="s">
         <v>192</v>
       </c>
@@ -16784,7 +16790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="33" t="s">
         <v>192</v>
       </c>
@@ -16818,7 +16824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="33" t="s">
         <v>192</v>
       </c>
@@ -16852,7 +16858,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="33" t="s">
         <v>192</v>
       </c>
@@ -16886,7 +16892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="33" t="s">
         <v>192</v>
       </c>
@@ -16920,7 +16926,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="33" t="s">
         <v>192</v>
       </c>
@@ -16954,7 +16960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="33" t="s">
         <v>192</v>
       </c>
@@ -16988,7 +16994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="33" t="s">
         <v>192</v>
       </c>
@@ -17022,7 +17028,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="33" t="s">
         <v>192</v>
       </c>
@@ -17056,7 +17062,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="33" t="s">
         <v>192</v>
       </c>
@@ -17090,7 +17096,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="33" t="s">
         <v>192</v>
       </c>
@@ -17124,7 +17130,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="33" t="s">
         <v>192</v>
       </c>
@@ -17158,7 +17164,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="33" t="s">
         <v>192</v>
       </c>
@@ -17192,7 +17198,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="33" t="s">
         <v>192</v>
       </c>
@@ -17226,7 +17232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="33" t="s">
         <v>192</v>
       </c>
@@ -17260,7 +17266,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="33" t="s">
         <v>192</v>
       </c>
@@ -17294,7 +17300,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="33" t="s">
         <v>192</v>
       </c>
@@ -17328,7 +17334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="33" t="s">
         <v>192</v>
       </c>
@@ -17362,7 +17368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="33" t="s">
         <v>192</v>
       </c>
@@ -17396,7 +17402,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="33" t="s">
         <v>192</v>
       </c>
@@ -17430,7 +17436,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="33" t="s">
         <v>192</v>
       </c>
@@ -17464,7 +17470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="33" t="s">
         <v>192</v>
       </c>
@@ -17498,7 +17504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="33" t="s">
         <v>192</v>
       </c>
@@ -17532,7 +17538,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="33" t="s">
         <v>192</v>
       </c>
@@ -17566,7 +17572,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="33" t="s">
         <v>192</v>
       </c>
@@ -17600,7 +17606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="33" t="s">
         <v>192</v>
       </c>
@@ -17634,7 +17640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="33" t="s">
         <v>192</v>
       </c>
@@ -17668,7 +17674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="33" t="s">
         <v>192</v>
       </c>
@@ -17702,7 +17708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="33" t="s">
         <v>192</v>
       </c>
@@ -17736,7 +17742,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="33" t="s">
         <v>192</v>
       </c>
@@ -17770,7 +17776,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="33" t="s">
         <v>192</v>
       </c>
@@ -17804,7 +17810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="33" t="s">
         <v>192</v>
       </c>
@@ -17838,7 +17844,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="33" t="s">
         <v>192</v>
       </c>
@@ -17872,7 +17878,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="33" t="s">
         <v>192</v>
       </c>
@@ -17906,7 +17912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="33" t="s">
         <v>192</v>
       </c>
@@ -17940,7 +17946,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="33" t="s">
         <v>192</v>
       </c>
@@ -17974,7 +17980,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="33" t="s">
         <v>192</v>
       </c>
@@ -18008,7 +18014,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="33" t="s">
         <v>192</v>
       </c>
@@ -18042,7 +18048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="33" t="s">
         <v>192</v>
       </c>
@@ -18076,7 +18082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="33" t="s">
         <v>192</v>
       </c>
@@ -18110,7 +18116,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="33" t="s">
         <v>192</v>
       </c>
@@ -18144,7 +18150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="33" t="s">
         <v>192</v>
       </c>
@@ -18178,7 +18184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="33" t="s">
         <v>192</v>
       </c>
@@ -18212,7 +18218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="33" t="s">
         <v>192</v>
       </c>
@@ -18246,7 +18252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="33" t="s">
         <v>192</v>
       </c>
@@ -18280,7 +18286,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="33" t="s">
         <v>192</v>
       </c>
@@ -18314,7 +18320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="33" t="s">
         <v>192</v>
       </c>
@@ -18348,7 +18354,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="33" t="s">
         <v>192</v>
       </c>
@@ -18382,7 +18388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="33" t="s">
         <v>192</v>
       </c>
@@ -18416,7 +18422,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="33" t="s">
         <v>192</v>
       </c>
@@ -18450,7 +18456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="33" t="s">
         <v>192</v>
       </c>
@@ -18484,7 +18490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="33" t="s">
         <v>192</v>
       </c>
@@ -18518,7 +18524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="33" t="s">
         <v>192</v>
       </c>
@@ -18552,7 +18558,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="33" t="s">
         <v>192</v>
       </c>
@@ -18586,7 +18592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="33" t="s">
         <v>192</v>
       </c>
@@ -18620,7 +18626,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="33" t="s">
         <v>192</v>
       </c>
@@ -18654,7 +18660,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="33" t="s">
         <v>192</v>
       </c>
@@ -18688,7 +18694,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="33" t="s">
         <v>192</v>
       </c>
@@ -18722,7 +18728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="33" t="s">
         <v>192</v>
       </c>
@@ -18756,7 +18762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="33" t="s">
         <v>192</v>
       </c>
@@ -18790,7 +18796,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="33" t="s">
         <v>192</v>
       </c>
@@ -18824,7 +18830,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="33" t="s">
         <v>192</v>
       </c>
@@ -18858,7 +18864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="33" t="s">
         <v>192</v>
       </c>
@@ -18892,7 +18898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="33" t="s">
         <v>188</v>
       </c>
@@ -18926,7 +18932,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="33" t="s">
         <v>188</v>
       </c>
@@ -18960,7 +18966,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="33" t="s">
         <v>188</v>
       </c>
@@ -18994,7 +19000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="33" t="s">
         <v>188</v>
       </c>
@@ -19028,7 +19034,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="33" t="s">
         <v>188</v>
       </c>
@@ -19062,7 +19068,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="33" t="s">
         <v>188</v>
       </c>
@@ -19096,7 +19102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="33" t="s">
         <v>188</v>
       </c>
@@ -19130,7 +19136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="33" t="s">
         <v>188</v>
       </c>
@@ -19164,7 +19170,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="33" t="s">
         <v>188</v>
       </c>
@@ -19198,7 +19204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="33" t="s">
         <v>188</v>
       </c>
@@ -19232,7 +19238,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="33" t="s">
         <v>188</v>
       </c>
@@ -19266,7 +19272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="33" t="s">
         <v>188</v>
       </c>
@@ -19300,7 +19306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="33" t="s">
         <v>188</v>
       </c>
@@ -19334,7 +19340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="33" t="s">
         <v>188</v>
       </c>
@@ -19368,7 +19374,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="33" t="s">
         <v>188</v>
       </c>
@@ -19402,7 +19408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="33" t="s">
         <v>188</v>
       </c>
@@ -19436,7 +19442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="33" t="s">
         <v>188</v>
       </c>
@@ -19470,7 +19476,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="33" t="s">
         <v>188</v>
       </c>
@@ -19504,7 +19510,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="33" t="s">
         <v>188</v>
       </c>
@@ -19538,7 +19544,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="33" t="s">
         <v>188</v>
       </c>
@@ -19572,7 +19578,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="33" t="s">
         <v>188</v>
       </c>
@@ -19606,7 +19612,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="33" t="s">
         <v>188</v>
       </c>
@@ -19640,7 +19646,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="33" t="s">
         <v>188</v>
       </c>
@@ -19674,7 +19680,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="33" t="s">
         <v>188</v>
       </c>
@@ -19708,7 +19714,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="33" t="s">
         <v>188</v>
       </c>
@@ -19742,7 +19748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="33" t="s">
         <v>188</v>
       </c>
@@ -19776,7 +19782,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="33" t="s">
         <v>188</v>
       </c>
@@ -19810,7 +19816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="33" t="s">
         <v>188</v>
       </c>
@@ -19844,7 +19850,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="33" t="s">
         <v>188</v>
       </c>
@@ -19878,7 +19884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="33" t="s">
         <v>188</v>
       </c>
@@ -19912,7 +19918,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="33" t="s">
         <v>188</v>
       </c>
@@ -19946,7 +19952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="33" t="s">
         <v>188</v>
       </c>
@@ -19980,7 +19986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="33" t="s">
         <v>188</v>
       </c>
@@ -20014,7 +20020,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="33" t="s">
         <v>188</v>
       </c>
@@ -20048,7 +20054,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="33" t="s">
         <v>188</v>
       </c>
@@ -20082,7 +20088,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="33" t="s">
         <v>188</v>
       </c>
@@ -20116,7 +20122,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="33" t="s">
         <v>188</v>
       </c>
@@ -20150,7 +20156,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="33" t="s">
         <v>188</v>
       </c>
@@ -20184,7 +20190,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="33" t="s">
         <v>188</v>
       </c>
@@ -20218,7 +20224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A294" s="33" t="s">
         <v>188</v>
       </c>
@@ -20252,7 +20258,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A295" s="33" t="s">
         <v>188</v>
       </c>
@@ -20286,7 +20292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A296" s="33" t="s">
         <v>188</v>
       </c>
@@ -20320,7 +20326,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A297" s="33" t="s">
         <v>188</v>
       </c>
@@ -20354,7 +20360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A298" s="33" t="s">
         <v>188</v>
       </c>
@@ -20388,7 +20394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="33" t="s">
         <v>188</v>
       </c>
@@ -20422,7 +20428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="33" t="s">
         <v>188</v>
       </c>
@@ -20456,7 +20462,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="33" t="s">
         <v>188</v>
       </c>
@@ -20490,7 +20496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="33" t="s">
         <v>188</v>
       </c>
@@ -20524,7 +20530,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="33" t="s">
         <v>188</v>
       </c>
@@ -20558,7 +20564,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="33" t="s">
         <v>188</v>
       </c>
@@ -20592,7 +20598,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="33" t="s">
         <v>188</v>
       </c>
@@ -20626,7 +20632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="33" t="s">
         <v>188</v>
       </c>
@@ -20660,7 +20666,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="33" t="s">
         <v>188</v>
       </c>
@@ -20694,7 +20700,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="33" t="s">
         <v>188</v>
       </c>
@@ -20728,7 +20734,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="33" t="s">
         <v>188</v>
       </c>
@@ -20762,7 +20768,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="33" t="s">
         <v>188</v>
       </c>
@@ -20796,7 +20802,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="33" t="s">
         <v>188</v>
       </c>
@@ -20830,7 +20836,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="33" t="s">
         <v>188</v>
       </c>
@@ -20864,7 +20870,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="33" t="s">
         <v>188</v>
       </c>
@@ -20898,7 +20904,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="33" t="s">
         <v>188</v>
       </c>
@@ -21068,7 +21074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="33" t="s">
         <v>195</v>
       </c>
@@ -21102,7 +21108,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="33" t="s">
         <v>195</v>
       </c>
@@ -21136,7 +21142,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="33" t="s">
         <v>195</v>
       </c>
@@ -21170,7 +21176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="33" t="s">
         <v>195</v>
       </c>
@@ -21204,7 +21210,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="33" t="s">
         <v>195</v>
       </c>
@@ -21238,7 +21244,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="33" t="s">
         <v>195</v>
       </c>
@@ -21272,7 +21278,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="33" t="s">
         <v>195</v>
       </c>
@@ -21306,7 +21312,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="33" t="s">
         <v>195</v>
       </c>
@@ -21340,7 +21346,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="33" t="s">
         <v>195</v>
       </c>
@@ -21374,7 +21380,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="33" t="s">
         <v>195</v>
       </c>
@@ -21408,7 +21414,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="33" t="s">
         <v>195</v>
       </c>
@@ -21442,7 +21448,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="33" t="s">
         <v>195</v>
       </c>
@@ -21476,7 +21482,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="33" t="s">
         <v>195</v>
       </c>
@@ -21510,7 +21516,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="33" t="s">
         <v>195</v>
       </c>
@@ -21544,7 +21550,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="33" t="s">
         <v>195</v>
       </c>
@@ -21578,7 +21584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="33" t="s">
         <v>195</v>
       </c>
@@ -21612,7 +21618,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="33" t="s">
         <v>195</v>
       </c>
@@ -21646,7 +21652,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="33" t="s">
         <v>195</v>
       </c>
@@ -21680,7 +21686,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="33" t="s">
         <v>195</v>
       </c>
@@ -21714,7 +21720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="33" t="s">
         <v>195</v>
       </c>
@@ -21748,7 +21754,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="33" t="s">
         <v>195</v>
       </c>
@@ -21782,7 +21788,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="33" t="s">
         <v>195</v>
       </c>
@@ -21816,7 +21822,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="33" t="s">
         <v>195</v>
       </c>
@@ -21850,7 +21856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="33" t="s">
         <v>195</v>
       </c>
@@ -21884,7 +21890,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="33" t="s">
         <v>195</v>
       </c>
@@ -21918,7 +21924,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="33" t="s">
         <v>195</v>
       </c>
@@ -21952,7 +21958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="33" t="s">
         <v>195</v>
       </c>
@@ -21986,7 +21992,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="33" t="s">
         <v>195</v>
       </c>
@@ -22020,7 +22026,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="33" t="s">
         <v>195</v>
       </c>
@@ -22054,7 +22060,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="33" t="s">
         <v>195</v>
       </c>
@@ -22088,7 +22094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="33" t="s">
         <v>195</v>
       </c>
@@ -22122,7 +22128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="33" t="s">
         <v>195</v>
       </c>
@@ -22156,7 +22162,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="33" t="s">
         <v>195</v>
       </c>
@@ -22190,7 +22196,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="33" t="s">
         <v>195</v>
       </c>
@@ -22224,7 +22230,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="33" t="s">
         <v>195</v>
       </c>
@@ -22258,7 +22264,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="33" t="s">
         <v>195</v>
       </c>
@@ -22292,7 +22298,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="33" t="s">
         <v>195</v>
       </c>
@@ -22326,7 +22332,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="33" t="s">
         <v>195</v>
       </c>
@@ -22360,7 +22366,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="33" t="s">
         <v>195</v>
       </c>
@@ -22394,7 +22400,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="33" t="s">
         <v>195</v>
       </c>
@@ -22428,7 +22434,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="33" t="s">
         <v>195</v>
       </c>
@@ -22462,7 +22468,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="33" t="s">
         <v>195</v>
       </c>
@@ -22496,7 +22502,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="33" t="s">
         <v>195</v>
       </c>
@@ -22530,7 +22536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="33" t="s">
         <v>195</v>
       </c>
@@ -22564,7 +22570,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="33" t="s">
         <v>195</v>
       </c>
@@ -22598,7 +22604,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="33" t="s">
         <v>195</v>
       </c>
@@ -22632,7 +22638,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="33" t="s">
         <v>195</v>
       </c>
@@ -22666,7 +22672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="33" t="s">
         <v>195</v>
       </c>
@@ -22700,7 +22706,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="33" t="s">
         <v>195</v>
       </c>
@@ -22734,7 +22740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="33" t="s">
         <v>195</v>
       </c>
@@ -22768,7 +22774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="33" t="s">
         <v>195</v>
       </c>
@@ -22802,7 +22808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="33" t="s">
         <v>195</v>
       </c>
@@ -22836,7 +22842,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="33" t="s">
         <v>195</v>
       </c>
@@ -22870,7 +22876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="33" t="s">
         <v>195</v>
       </c>
@@ -22904,7 +22910,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="33" t="s">
         <v>195</v>
       </c>
@@ -22938,7 +22944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="33" t="s">
         <v>195</v>
       </c>
@@ -22972,7 +22978,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="33" t="s">
         <v>195</v>
       </c>
@@ -23006,7 +23012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="33" t="s">
         <v>195</v>
       </c>
@@ -23040,7 +23046,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="33" t="s">
         <v>195</v>
       </c>
@@ -23074,7 +23080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="33" t="s">
         <v>195</v>
       </c>
@@ -23108,7 +23114,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="33" t="s">
         <v>195</v>
       </c>
@@ -23142,7 +23148,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="33" t="s">
         <v>195</v>
       </c>
@@ -23176,7 +23182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="33" t="s">
         <v>195</v>
       </c>
@@ -23210,7 +23216,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="33" t="s">
         <v>195</v>
       </c>
@@ -23244,7 +23250,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="33" t="s">
         <v>195</v>
       </c>
@@ -23278,7 +23284,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="33" t="s">
         <v>195</v>
       </c>
@@ -23312,7 +23318,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="33" t="s">
         <v>195</v>
       </c>
@@ -23346,7 +23352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="33" t="s">
         <v>195</v>
       </c>
@@ -23380,7 +23386,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="33" t="s">
         <v>194</v>
       </c>
@@ -23414,7 +23420,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="33" t="s">
         <v>194</v>
       </c>
@@ -23448,7 +23454,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="389" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="33" t="s">
         <v>194</v>
       </c>
@@ -23482,7 +23488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="33" t="s">
         <v>194</v>
       </c>
@@ -23516,7 +23522,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="33" t="s">
         <v>194</v>
       </c>
@@ -23550,7 +23556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="33" t="s">
         <v>194</v>
       </c>
@@ -23584,7 +23590,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="33" t="s">
         <v>194</v>
       </c>
@@ -23618,7 +23624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="33" t="s">
         <v>194</v>
       </c>
@@ -23652,7 +23658,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="33" t="s">
         <v>194</v>
       </c>
@@ -23686,7 +23692,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="33" t="s">
         <v>194</v>
       </c>
@@ -23720,7 +23726,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="33" t="s">
         <v>194</v>
       </c>
@@ -23754,7 +23760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="33" t="s">
         <v>194</v>
       </c>
@@ -23788,7 +23794,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="33" t="s">
         <v>194</v>
       </c>
@@ -23822,7 +23828,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="33" t="s">
         <v>194</v>
       </c>
@@ -23856,7 +23862,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="33" t="s">
         <v>194</v>
       </c>
@@ -23890,7 +23896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="33" t="s">
         <v>194</v>
       </c>
@@ -23924,7 +23930,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="403" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="33" t="s">
         <v>194</v>
       </c>
@@ -23958,7 +23964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="404" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="33" t="s">
         <v>194</v>
       </c>
@@ -23992,7 +23998,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="33" t="s">
         <v>194</v>
       </c>
@@ -24026,7 +24032,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="33" t="s">
         <v>194</v>
       </c>
@@ -24060,7 +24066,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="33" t="s">
         <v>194</v>
       </c>
@@ -24094,7 +24100,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="33" t="s">
         <v>194</v>
       </c>
@@ -24128,7 +24134,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="33" t="s">
         <v>194</v>
       </c>
@@ -24162,7 +24168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="33" t="s">
         <v>194</v>
       </c>
@@ -24196,7 +24202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="33" t="s">
         <v>194</v>
       </c>
@@ -24230,7 +24236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="33" t="s">
         <v>194</v>
       </c>
@@ -24264,7 +24270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="33" t="s">
         <v>194</v>
       </c>
@@ -24298,7 +24304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="33" t="s">
         <v>194</v>
       </c>
@@ -24332,7 +24338,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="33" t="s">
         <v>194</v>
       </c>
@@ -24366,7 +24372,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="33" t="s">
         <v>194</v>
       </c>
@@ -24400,7 +24406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="33" t="s">
         <v>194</v>
       </c>
@@ -24434,7 +24440,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="33" t="s">
         <v>194</v>
       </c>
@@ -24468,7 +24474,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="33" t="s">
         <v>194</v>
       </c>
@@ -24502,7 +24508,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="33" t="s">
         <v>194</v>
       </c>
@@ -24536,7 +24542,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="33" t="s">
         <v>194</v>
       </c>
@@ -24570,7 +24576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="33" t="s">
         <v>194</v>
       </c>
@@ -24604,7 +24610,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="33" t="s">
         <v>194</v>
       </c>
@@ -24638,7 +24644,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="33" t="s">
         <v>194</v>
       </c>
@@ -24672,7 +24678,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="33" t="s">
         <v>194</v>
       </c>
@@ -24706,7 +24712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="33" t="s">
         <v>194</v>
       </c>
@@ -24740,7 +24746,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="33" t="s">
         <v>194</v>
       </c>
@@ -24774,7 +24780,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="33" t="s">
         <v>194</v>
       </c>
@@ -24808,7 +24814,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="33" t="s">
         <v>194</v>
       </c>
@@ -24842,7 +24848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="33" t="s">
         <v>194</v>
       </c>
@@ -24876,7 +24882,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="33" t="s">
         <v>194</v>
       </c>
@@ -24910,7 +24916,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="33" t="s">
         <v>194</v>
       </c>
@@ -24944,7 +24950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="33" t="s">
         <v>194</v>
       </c>
@@ -24978,7 +24984,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="33" t="s">
         <v>194</v>
       </c>
@@ -25012,7 +25018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="33" t="s">
         <v>190</v>
       </c>
@@ -25046,7 +25052,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="33" t="s">
         <v>190</v>
       </c>
@@ -25080,7 +25086,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="33" t="s">
         <v>190</v>
       </c>
@@ -25114,7 +25120,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="33" t="s">
         <v>190</v>
       </c>
@@ -25148,7 +25154,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="33" t="s">
         <v>190</v>
       </c>
@@ -25182,7 +25188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="33" t="s">
         <v>190</v>
       </c>
@@ -25216,7 +25222,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="33" t="s">
         <v>190</v>
       </c>
@@ -25250,7 +25256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="33" t="s">
         <v>190</v>
       </c>
@@ -25284,7 +25290,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="33" t="s">
         <v>190</v>
       </c>
@@ -25318,7 +25324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="33" t="s">
         <v>190</v>
       </c>
@@ -25352,7 +25358,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="33" t="s">
         <v>190</v>
       </c>
@@ -25386,7 +25392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="33" t="s">
         <v>190</v>
       </c>
@@ -25420,7 +25426,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="33" t="s">
         <v>190</v>
       </c>
@@ -25454,7 +25460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="33" t="s">
         <v>190</v>
       </c>
@@ -25488,7 +25494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="33" t="s">
         <v>190</v>
       </c>
@@ -25522,7 +25528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="33" t="s">
         <v>190</v>
       </c>
@@ -25556,7 +25562,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="33" t="s">
         <v>190</v>
       </c>
@@ -25590,7 +25596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="33" t="s">
         <v>190</v>
       </c>
@@ -25624,7 +25630,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="33" t="s">
         <v>190</v>
       </c>
@@ -25658,7 +25664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="33" t="s">
         <v>190</v>
       </c>
@@ -25692,7 +25698,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="33" t="s">
         <v>190</v>
       </c>
@@ -25726,7 +25732,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="33" t="s">
         <v>190</v>
       </c>
@@ -25760,7 +25766,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="33" t="s">
         <v>190</v>
       </c>
@@ -25794,7 +25800,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="33" t="s">
         <v>190</v>
       </c>
@@ -25828,7 +25834,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="459" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="33" t="s">
         <v>190</v>
       </c>
@@ -25862,7 +25868,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="33" t="s">
         <v>190</v>
       </c>
@@ -25896,7 +25902,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="33" t="s">
         <v>190</v>
       </c>
@@ -25930,7 +25936,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="33" t="s">
         <v>190</v>
       </c>
@@ -25964,7 +25970,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="33" t="s">
         <v>190</v>
       </c>
@@ -25998,7 +26004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="33" t="s">
         <v>190</v>
       </c>
@@ -26032,7 +26038,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="33" t="s">
         <v>190</v>
       </c>
@@ -26066,7 +26072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="33" t="s">
         <v>190</v>
       </c>
@@ -26100,7 +26106,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="33" t="s">
         <v>193</v>
       </c>
@@ -26134,7 +26140,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="33" t="s">
         <v>193</v>
       </c>
@@ -26168,7 +26174,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="469" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="33" t="s">
         <v>193</v>
       </c>
@@ -26202,7 +26208,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="33" t="s">
         <v>193</v>
       </c>
@@ -26236,7 +26242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="471" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="33" t="s">
         <v>193</v>
       </c>
@@ -26270,7 +26276,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="33" t="s">
         <v>193</v>
       </c>
@@ -26304,7 +26310,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="33" t="s">
         <v>193</v>
       </c>
@@ -26338,7 +26344,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="33" t="s">
         <v>193</v>
       </c>
@@ -26372,7 +26378,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="33" t="s">
         <v>193</v>
       </c>
@@ -26406,7 +26412,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="33" t="s">
         <v>193</v>
       </c>
@@ -26440,7 +26446,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="33" t="s">
         <v>193</v>
       </c>
@@ -26474,7 +26480,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="33" t="s">
         <v>193</v>
       </c>
@@ -26508,7 +26514,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="33" t="s">
         <v>193</v>
       </c>
@@ -26542,7 +26548,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="33" t="s">
         <v>193</v>
       </c>
@@ -26576,7 +26582,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="33" t="s">
         <v>193</v>
       </c>
@@ -26610,7 +26616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="33" t="s">
         <v>193</v>
       </c>
@@ -26644,7 +26650,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="33" t="s">
         <v>193</v>
       </c>
@@ -26678,7 +26684,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="33" t="s">
         <v>193</v>
       </c>
@@ -26712,7 +26718,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="33" t="s">
         <v>193</v>
       </c>
@@ -26746,7 +26752,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="33" t="s">
         <v>193</v>
       </c>
@@ -26780,7 +26786,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="33" t="s">
         <v>193</v>
       </c>
@@ -26814,7 +26820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="33" t="s">
         <v>193</v>
       </c>
@@ -26848,7 +26854,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="489" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="33" t="s">
         <v>193</v>
       </c>
@@ -26882,7 +26888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="490" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="33" t="s">
         <v>193</v>
       </c>
@@ -26916,7 +26922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="33" t="s">
         <v>193</v>
       </c>
@@ -26950,7 +26956,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="33" t="s">
         <v>193</v>
       </c>
@@ -26984,7 +26990,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="33" t="s">
         <v>193</v>
       </c>
@@ -27018,7 +27024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="33" t="s">
         <v>193</v>
       </c>
@@ -27052,7 +27058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="495" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="33" t="s">
         <v>193</v>
       </c>
@@ -27086,7 +27092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="33" t="s">
         <v>193</v>
       </c>
@@ -27120,7 +27126,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="33" t="s">
         <v>193</v>
       </c>
@@ -27154,7 +27160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="33" t="s">
         <v>193</v>
       </c>
@@ -27188,7 +27194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="33" t="s">
         <v>191</v>
       </c>
@@ -27222,7 +27228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="33" t="s">
         <v>191</v>
       </c>
@@ -27256,7 +27262,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="33" t="s">
         <v>191</v>
       </c>
@@ -27290,7 +27296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="33" t="s">
         <v>191</v>
       </c>
@@ -27324,7 +27330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="33" t="s">
         <v>191</v>
       </c>
@@ -27358,7 +27364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="33" t="s">
         <v>191</v>
       </c>
@@ -27392,7 +27398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="505" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="33" t="s">
         <v>191</v>
       </c>
@@ -27426,7 +27432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="506" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="33" t="s">
         <v>191</v>
       </c>
@@ -27460,7 +27466,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="33" t="s">
         <v>191</v>
       </c>
@@ -27494,7 +27500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="33" t="s">
         <v>191</v>
       </c>
@@ -27528,7 +27534,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="33" t="s">
         <v>191</v>
       </c>
@@ -27562,7 +27568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="33" t="s">
         <v>191</v>
       </c>
@@ -27596,7 +27602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="33" t="s">
         <v>191</v>
       </c>
@@ -27630,7 +27636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="33" t="s">
         <v>191</v>
       </c>
@@ -27664,7 +27670,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="33" t="s">
         <v>191</v>
       </c>
@@ -27698,7 +27704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="514" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="33" t="s">
         <v>191</v>
       </c>
@@ -27732,7 +27738,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="515" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="33" t="s">
         <v>191</v>
       </c>
@@ -27766,7 +27772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="33" t="s">
         <v>191</v>
       </c>
@@ -27800,7 +27806,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="517" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="33" t="s">
         <v>191</v>
       </c>
@@ -27834,7 +27840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="518" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="33" t="s">
         <v>191</v>
       </c>
@@ -27868,7 +27874,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="519" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="33" t="s">
         <v>191</v>
       </c>
@@ -27902,7 +27908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="33" t="s">
         <v>191</v>
       </c>
@@ -27936,7 +27942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="33" t="s">
         <v>191</v>
       </c>
@@ -27970,7 +27976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="33" t="s">
         <v>191</v>
       </c>
@@ -28004,7 +28010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="523" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="33" t="s">
         <v>191</v>
       </c>
@@ -28038,7 +28044,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="524" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="33" t="s">
         <v>191</v>
       </c>
@@ -28072,7 +28078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="525" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="33" t="s">
         <v>191</v>
       </c>
@@ -28106,7 +28112,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="526" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="33" t="s">
         <v>191</v>
       </c>
@@ -28140,7 +28146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="527" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="33" t="s">
         <v>191</v>
       </c>
@@ -28174,7 +28180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="528" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="33" t="s">
         <v>191</v>
       </c>
@@ -28208,7 +28214,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="529" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="33" t="s">
         <v>191</v>
       </c>
@@ -28242,7 +28248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="33" t="s">
         <v>191</v>
       </c>
@@ -28279,7 +28285,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="531" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="33" t="s">
         <v>191</v>
       </c>
@@ -28313,7 +28319,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="532" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="33" t="s">
         <v>191</v>
       </c>
@@ -28347,7 +28353,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="533" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="33" t="s">
         <v>191</v>
       </c>
@@ -28381,7 +28387,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="534" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="33" t="s">
         <v>191</v>
       </c>
@@ -28415,7 +28421,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="535" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="33" t="s">
         <v>191</v>
       </c>
@@ -28449,7 +28455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="536" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="33" t="s">
         <v>191</v>
       </c>
@@ -28483,7 +28489,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="537" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="33" t="s">
         <v>191</v>
       </c>
@@ -28517,7 +28523,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="538" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="33" t="s">
         <v>191</v>
       </c>
@@ -28551,7 +28557,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="539" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="33" t="s">
         <v>191</v>
       </c>
@@ -28585,7 +28591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="540" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="33" t="s">
         <v>191</v>
       </c>
@@ -28619,7 +28625,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="541" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="33" t="s">
         <v>191</v>
       </c>
@@ -28653,7 +28659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="33" t="s">
         <v>191</v>
       </c>
@@ -28687,7 +28693,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="543" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="33" t="s">
         <v>191</v>
       </c>
@@ -28721,7 +28727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="33" t="s">
         <v>191</v>
       </c>
@@ -28755,7 +28761,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="33" t="s">
         <v>191</v>
       </c>
@@ -28789,7 +28795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="33" t="s">
         <v>191</v>
       </c>
@@ -28823,7 +28829,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="547" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="33" t="s">
         <v>191</v>
       </c>
@@ -28857,7 +28863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="33" t="s">
         <v>191</v>
       </c>
@@ -28891,7 +28897,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="549" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="33" t="s">
         <v>191</v>
       </c>
@@ -28925,7 +28931,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="33" t="s">
         <v>191</v>
       </c>
@@ -28959,7 +28965,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="33" t="s">
         <v>191</v>
       </c>
@@ -28993,7 +28999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="33" t="s">
         <v>191</v>
       </c>
@@ -29027,7 +29033,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="553" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="33" t="s">
         <v>191</v>
       </c>
@@ -29061,7 +29067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="554" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="33" t="s">
         <v>191</v>
       </c>
@@ -29095,7 +29101,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="555" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="33" t="s">
         <v>191</v>
       </c>
@@ -29129,7 +29135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="556" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="33" t="s">
         <v>191</v>
       </c>
@@ -29163,7 +29169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="33" t="s">
         <v>191</v>
       </c>
@@ -29197,7 +29203,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="558" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="33" t="s">
         <v>191</v>
       </c>
@@ -29231,7 +29237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="559" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="33" t="s">
         <v>191</v>
       </c>
@@ -29265,7 +29271,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="560" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="33" t="s">
         <v>191</v>
       </c>
@@ -29299,7 +29305,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="561" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="33" t="s">
         <v>191</v>
       </c>
@@ -29333,7 +29339,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="562" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="33" t="s">
         <v>191</v>
       </c>
@@ -29367,7 +29373,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="563" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="33" t="s">
         <v>191</v>
       </c>
@@ -29401,7 +29407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="564" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="33" t="s">
         <v>191</v>
       </c>
@@ -29435,7 +29441,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="565" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="33" t="s">
         <v>191</v>
       </c>
@@ -29469,7 +29475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="33" t="s">
         <v>191</v>
       </c>
@@ -29503,7 +29509,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="567" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="33" t="s">
         <v>191</v>
       </c>
@@ -29537,7 +29543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="568" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="33" t="s">
         <v>191</v>
       </c>
@@ -29571,7 +29577,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="33" t="s">
         <v>191</v>
       </c>
@@ -29605,7 +29611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="570" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="33" t="s">
         <v>191</v>
       </c>
@@ -29639,7 +29645,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="571" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="33" t="s">
         <v>191</v>
       </c>
@@ -29673,7 +29679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="572" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="33" t="s">
         <v>191</v>
       </c>
@@ -29707,7 +29713,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="573" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="33" t="s">
         <v>191</v>
       </c>
@@ -29741,7 +29747,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="574" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="33" t="s">
         <v>191</v>
       </c>
@@ -29775,7 +29781,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="575" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="33" t="s">
         <v>191</v>
       </c>
@@ -29809,7 +29815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="576" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="33" t="s">
         <v>191</v>
       </c>
@@ -29843,7 +29849,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="577" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="33" t="s">
         <v>191</v>
       </c>
@@ -29877,7 +29883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="578" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="33" t="s">
         <v>191</v>
       </c>
@@ -29912,13 +29918,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L578" xr:uid="{CF8D923C-FBE4-455B-BC9C-7957F0721F03}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="CHASI TINE JOSE IGNACIO/JOSEDEL S.A"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:L578" xr:uid="{CF8D923C-FBE4-455B-BC9C-7957F0721F03}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
